--- a/planillas/planilla_columnas.xlsx
+++ b/planillas/planilla_columnas.xlsx
@@ -991,7 +991,9 @@
       <c r="C4" s="14" t="n">
         <v>3.22</v>
       </c>
-      <c r="D4" s="15" t="n"/>
+      <c r="D4" s="15" t="n">
+        <v>14.25</v>
+      </c>
       <c r="E4" s="16" t="n">
         <v>20</v>
       </c>
@@ -1020,12 +1022,12 @@
         <v/>
       </c>
       <c r="M4" s="6">
-        <f>IF(D4="","FALTA CARGA",IF(O4&lt;H4,"ARM. INSUFIC.",IF(D4&gt;P4,"NO VERIFICA",IF(Q4&gt;34,"VERIF. ESBELTEZ","VERIFICA"))))</f>
+        <f>IF(D4="","FALTA CARGA",IF(O4&lt;H4,"ARM. INSUFIC.",IF(D4&gt;P4,"NO VERIFICA",IF(D4&gt;0.85*P4,"AL LIMITE",IF(Q4&gt;34,"VERIF. ESBELTEZ","VERIFICA")))))</f>
         <v/>
       </c>
       <c r="N4" s="18" t="inlineStr">
         <is>
-          <t>COL 07 del plano. Carga estimada por bajada automatica: 14.3 t (incompleta, ver Memoria).</t>
+          <t>COL 07 del plano. Carga PROVISORIA por bajada automatica; es un piso, la real es mayor (ver Memoria, punto 5).</t>
         </is>
       </c>
       <c r="O4" s="19">
@@ -1054,7 +1056,9 @@
       <c r="C5" s="14" t="n">
         <v>3.22</v>
       </c>
-      <c r="D5" s="15" t="n"/>
+      <c r="D5" s="15" t="n">
+        <v>17.23</v>
+      </c>
       <c r="E5" s="16" t="n">
         <v>30</v>
       </c>
@@ -1083,12 +1087,12 @@
         <v/>
       </c>
       <c r="M5" s="6">
-        <f>IF(D5="","FALTA CARGA",IF(O5&lt;H5,"ARM. INSUFIC.",IF(D5&gt;P5,"NO VERIFICA",IF(Q5&gt;34,"VERIF. ESBELTEZ","VERIFICA"))))</f>
+        <f>IF(D5="","FALTA CARGA",IF(O5&lt;H5,"ARM. INSUFIC.",IF(D5&gt;P5,"NO VERIFICA",IF(D5&gt;0.85*P5,"AL LIMITE",IF(Q5&gt;34,"VERIF. ESBELTEZ","VERIFICA")))))</f>
         <v/>
       </c>
       <c r="N5" s="18" t="inlineStr">
         <is>
-          <t>COL 06 del plano. Carga estimada por bajada automatica: 17.2 t (incompleta, ver Memoria).</t>
+          <t>COL 06 del plano. Carga PROVISORIA por bajada automatica; es un piso, la real es mayor (ver Memoria, punto 5).</t>
         </is>
       </c>
       <c r="O5" s="19">
@@ -1117,7 +1121,9 @@
       <c r="C6" s="14" t="n">
         <v>3.22</v>
       </c>
-      <c r="D6" s="15" t="n"/>
+      <c r="D6" s="15" t="n">
+        <v>18.5</v>
+      </c>
       <c r="E6" s="16" t="n">
         <v>15</v>
       </c>
@@ -1146,12 +1152,12 @@
         <v/>
       </c>
       <c r="M6" s="6">
-        <f>IF(D6="","FALTA CARGA",IF(O6&lt;H6,"ARM. INSUFIC.",IF(D6&gt;P6,"NO VERIFICA",IF(Q6&gt;34,"VERIF. ESBELTEZ","VERIFICA"))))</f>
+        <f>IF(D6="","FALTA CARGA",IF(O6&lt;H6,"ARM. INSUFIC.",IF(D6&gt;P6,"NO VERIFICA",IF(D6&gt;0.85*P6,"AL LIMITE",IF(Q6&gt;34,"VERIF. ESBELTEZ","VERIFICA")))))</f>
         <v/>
       </c>
       <c r="N6" s="18" t="inlineStr">
         <is>
-          <t>COL 05 del plano. Carga estimada por bajada automatica: 18.5 t (incompleta, ver Memoria).</t>
+          <t>COL 05 del plano. Carga PROVISORIA por bajada automatica; es un piso, la real es mayor (ver Memoria, punto 5).</t>
         </is>
       </c>
       <c r="O6" s="19">
@@ -1180,7 +1186,9 @@
       <c r="C7" s="24" t="n">
         <v>3.22</v>
       </c>
-      <c r="D7" s="25" t="n"/>
+      <c r="D7" s="25" t="n">
+        <v>19.44</v>
+      </c>
       <c r="E7" s="26" t="n">
         <v>15</v>
       </c>
@@ -1209,12 +1217,12 @@
         <v/>
       </c>
       <c r="M7" s="27">
-        <f>IF(D7="","FALTA CARGA",IF(O7&lt;H7,"ARM. INSUFIC.",IF(D7&gt;P7,"NO VERIFICA",IF(Q7&gt;34,"VERIF. ESBELTEZ","VERIFICA"))))</f>
+        <f>IF(D7="","FALTA CARGA",IF(O7&lt;H7,"ARM. INSUFIC.",IF(D7&gt;P7,"NO VERIFICA",IF(D7&gt;0.85*P7,"AL LIMITE",IF(Q7&gt;34,"VERIF. ESBELTEZ","VERIFICA")))))</f>
         <v/>
       </c>
       <c r="N7" s="29" t="inlineStr">
         <is>
-          <t>COL 05 del plano. Carga estimada por bajada automatica: 19.4 t (incompleta, ver Memoria).</t>
+          <t>COL 05 del plano. Carga PROVISORIA por bajada automatica; es un piso, la real es mayor (ver Memoria, punto 5).</t>
         </is>
       </c>
       <c r="O7" s="30">
@@ -1247,7 +1255,9 @@
       <c r="C8" s="14" t="n">
         <v>3.15</v>
       </c>
-      <c r="D8" s="15" t="n"/>
+      <c r="D8" s="15" t="n">
+        <v>6.38</v>
+      </c>
       <c r="E8" s="16" t="n">
         <v>15</v>
       </c>
@@ -1276,12 +1286,12 @@
         <v/>
       </c>
       <c r="M8" s="6">
-        <f>IF(D8="","FALTA CARGA",IF(O8&lt;H8,"ARM. INSUFIC.",IF(D8&gt;P8,"NO VERIFICA",IF(Q8&gt;34,"VERIF. ESBELTEZ","VERIFICA"))))</f>
+        <f>IF(D8="","FALTA CARGA",IF(O8&lt;H8,"ARM. INSUFIC.",IF(D8&gt;P8,"NO VERIFICA",IF(D8&gt;0.85*P8,"AL LIMITE",IF(Q8&gt;34,"VERIF. ESBELTEZ","VERIFICA")))))</f>
         <v/>
       </c>
       <c r="N8" s="18" t="inlineStr">
         <is>
-          <t>COL 02 del plano. Carga estimada por bajada automatica: 6.4 t (incompleta, ver Memoria).</t>
+          <t>COL 02 del plano. Carga PROVISORIA por bajada automatica; es un piso, la real es mayor (ver Memoria, punto 5).</t>
         </is>
       </c>
       <c r="O8" s="19">
@@ -1310,7 +1320,9 @@
       <c r="C9" s="14" t="n">
         <v>3.15</v>
       </c>
-      <c r="D9" s="15" t="n"/>
+      <c r="D9" s="15" t="n">
+        <v>36.41</v>
+      </c>
       <c r="E9" s="16" t="n">
         <v>15</v>
       </c>
@@ -1339,12 +1351,12 @@
         <v/>
       </c>
       <c r="M9" s="6">
-        <f>IF(D9="","FALTA CARGA",IF(O9&lt;H9,"ARM. INSUFIC.",IF(D9&gt;P9,"NO VERIFICA",IF(Q9&gt;34,"VERIF. ESBELTEZ","VERIFICA"))))</f>
+        <f>IF(D9="","FALTA CARGA",IF(O9&lt;H9,"ARM. INSUFIC.",IF(D9&gt;P9,"NO VERIFICA",IF(D9&gt;0.85*P9,"AL LIMITE",IF(Q9&gt;34,"VERIF. ESBELTEZ","VERIFICA")))))</f>
         <v/>
       </c>
       <c r="N9" s="18" t="inlineStr">
         <is>
-          <t>COL 02 del plano. Carga estimada por bajada automatica: 36.4 t (incompleta, ver Memoria).</t>
+          <t>COL 02 del plano. Carga PROVISORIA por bajada automatica; es un piso, la real es mayor (ver Memoria, punto 5).</t>
         </is>
       </c>
       <c r="O9" s="19">
@@ -1373,7 +1385,9 @@
       <c r="C10" s="14" t="n">
         <v>3.15</v>
       </c>
-      <c r="D10" s="15" t="n"/>
+      <c r="D10" s="15" t="n">
+        <v>19.85</v>
+      </c>
       <c r="E10" s="16" t="n">
         <v>30</v>
       </c>
@@ -1402,12 +1416,12 @@
         <v/>
       </c>
       <c r="M10" s="6">
-        <f>IF(D10="","FALTA CARGA",IF(O10&lt;H10,"ARM. INSUFIC.",IF(D10&gt;P10,"NO VERIFICA",IF(Q10&gt;34,"VERIF. ESBELTEZ","VERIFICA"))))</f>
+        <f>IF(D10="","FALTA CARGA",IF(O10&lt;H10,"ARM. INSUFIC.",IF(D10&gt;P10,"NO VERIFICA",IF(D10&gt;0.85*P10,"AL LIMITE",IF(Q10&gt;34,"VERIF. ESBELTEZ","VERIFICA")))))</f>
         <v/>
       </c>
       <c r="N10" s="18" t="inlineStr">
         <is>
-          <t>COL 03 del plano. Carga estimada por bajada automatica: 19.8 t (incompleta, ver Memoria).</t>
+          <t>COL 03 del plano. Carga PROVISORIA por bajada automatica; es un piso, la real es mayor (ver Memoria, punto 5).</t>
         </is>
       </c>
       <c r="O10" s="19">
@@ -1436,7 +1450,9 @@
       <c r="C11" s="14" t="n">
         <v>3.15</v>
       </c>
-      <c r="D11" s="15" t="n"/>
+      <c r="D11" s="15" t="n">
+        <v>28.77</v>
+      </c>
       <c r="E11" s="16" t="n">
         <v>10</v>
       </c>
@@ -1465,12 +1481,12 @@
         <v/>
       </c>
       <c r="M11" s="6">
-        <f>IF(D11="","FALTA CARGA",IF(O11&lt;H11,"ARM. INSUFIC.",IF(D11&gt;P11,"NO VERIFICA",IF(Q11&gt;34,"VERIF. ESBELTEZ","VERIFICA"))))</f>
+        <f>IF(D11="","FALTA CARGA",IF(O11&lt;H11,"ARM. INSUFIC.",IF(D11&gt;P11,"NO VERIFICA",IF(D11&gt;0.85*P11,"AL LIMITE",IF(Q11&gt;34,"VERIF. ESBELTEZ","VERIFICA")))))</f>
         <v/>
       </c>
       <c r="N11" s="18" t="inlineStr">
         <is>
-          <t>COL 01 del plano. Carga estimada por bajada automatica: 28.8 t (incompleta, ver Memoria). ATENCION: seccion 10x10 leida del plano. Recibe VI 01a (17 t): una columna de 10x10 no puede tomar esa carga. Probablemente VI 01a apoye en la medianera y esto no sea columna.</t>
+          <t>COL 01 del plano. Carga PROVISORIA por bajada automatica; es un piso, la real es mayor (ver Memoria, punto 5). ATENCION: seccion 10x10 leida del plano. Recibe VI 01a (17 t): una columna de 10x10 no puede tomar esa carga. Probablemente VI 01a apoye en la medianera y esto no sea columna.</t>
         </is>
       </c>
       <c r="O11" s="19">
@@ -1499,7 +1515,9 @@
       <c r="C12" s="14" t="n">
         <v>3.15</v>
       </c>
-      <c r="D12" s="15" t="n"/>
+      <c r="D12" s="15" t="n">
+        <v>20.2</v>
+      </c>
       <c r="E12" s="16" t="n">
         <v>15</v>
       </c>
@@ -1528,12 +1546,12 @@
         <v/>
       </c>
       <c r="M12" s="6">
-        <f>IF(D12="","FALTA CARGA",IF(O12&lt;H12,"ARM. INSUFIC.",IF(D12&gt;P12,"NO VERIFICA",IF(Q12&gt;34,"VERIF. ESBELTEZ","VERIFICA"))))</f>
+        <f>IF(D12="","FALTA CARGA",IF(O12&lt;H12,"ARM. INSUFIC.",IF(D12&gt;P12,"NO VERIFICA",IF(D12&gt;0.85*P12,"AL LIMITE",IF(Q12&gt;34,"VERIF. ESBELTEZ","VERIFICA")))))</f>
         <v/>
       </c>
       <c r="N12" s="18" t="inlineStr">
         <is>
-          <t>COL 02 del plano. Carga estimada por bajada automatica: 20.2 t (incompleta, ver Memoria).</t>
+          <t>COL 02 del plano. Carga PROVISORIA por bajada automatica; es un piso, la real es mayor (ver Memoria, punto 5).</t>
         </is>
       </c>
       <c r="O12" s="19">
@@ -1562,7 +1580,9 @@
       <c r="C13" s="14" t="n">
         <v>3.15</v>
       </c>
-      <c r="D13" s="15" t="n"/>
+      <c r="D13" s="15" t="n">
+        <v>43.36</v>
+      </c>
       <c r="E13" s="16" t="n">
         <v>20</v>
       </c>
@@ -1591,12 +1611,12 @@
         <v/>
       </c>
       <c r="M13" s="6">
-        <f>IF(D13="","FALTA CARGA",IF(O13&lt;H13,"ARM. INSUFIC.",IF(D13&gt;P13,"NO VERIFICA",IF(Q13&gt;34,"VERIF. ESBELTEZ","VERIFICA"))))</f>
+        <f>IF(D13="","FALTA CARGA",IF(O13&lt;H13,"ARM. INSUFIC.",IF(D13&gt;P13,"NO VERIFICA",IF(D13&gt;0.85*P13,"AL LIMITE",IF(Q13&gt;34,"VERIF. ESBELTEZ","VERIFICA")))))</f>
         <v/>
       </c>
       <c r="N13" s="18" t="inlineStr">
         <is>
-          <t>COL 04 del plano. Carga estimada por bajada automatica: 43.4 t (incompleta, ver Memoria).</t>
+          <t>COL 04 del plano. Carga PROVISORIA por bajada automatica; es un piso, la real es mayor (ver Memoria, punto 5).</t>
         </is>
       </c>
       <c r="O13" s="19">
@@ -1625,7 +1645,9 @@
       <c r="C14" s="14" t="n">
         <v>3.15</v>
       </c>
-      <c r="D14" s="15" t="n"/>
+      <c r="D14" s="15" t="n">
+        <v>32.38</v>
+      </c>
       <c r="E14" s="16" t="n">
         <v>30</v>
       </c>
@@ -1654,12 +1676,12 @@
         <v/>
       </c>
       <c r="M14" s="6">
-        <f>IF(D14="","FALTA CARGA",IF(O14&lt;H14,"ARM. INSUFIC.",IF(D14&gt;P14,"NO VERIFICA",IF(Q14&gt;34,"VERIF. ESBELTEZ","VERIFICA"))))</f>
+        <f>IF(D14="","FALTA CARGA",IF(O14&lt;H14,"ARM. INSUFIC.",IF(D14&gt;P14,"NO VERIFICA",IF(D14&gt;0.85*P14,"AL LIMITE",IF(Q14&gt;34,"VERIF. ESBELTEZ","VERIFICA")))))</f>
         <v/>
       </c>
       <c r="N14" s="18" t="inlineStr">
         <is>
-          <t>COL 03 del plano. Carga estimada por bajada automatica: 32.4 t (incompleta, ver Memoria).</t>
+          <t>COL 03 del plano. Carga PROVISORIA por bajada automatica; es un piso, la real es mayor (ver Memoria, punto 5).</t>
         </is>
       </c>
       <c r="O14" s="19">
@@ -1688,7 +1710,9 @@
       <c r="C15" s="14" t="n">
         <v>3.15</v>
       </c>
-      <c r="D15" s="15" t="n"/>
+      <c r="D15" s="15" t="n">
+        <v>42.14</v>
+      </c>
       <c r="E15" s="16" t="n">
         <v>15</v>
       </c>
@@ -1717,12 +1741,12 @@
         <v/>
       </c>
       <c r="M15" s="6">
-        <f>IF(D15="","FALTA CARGA",IF(O15&lt;H15,"ARM. INSUFIC.",IF(D15&gt;P15,"NO VERIFICA",IF(Q15&gt;34,"VERIF. ESBELTEZ","VERIFICA"))))</f>
+        <f>IF(D15="","FALTA CARGA",IF(O15&lt;H15,"ARM. INSUFIC.",IF(D15&gt;P15,"NO VERIFICA",IF(D15&gt;0.85*P15,"AL LIMITE",IF(Q15&gt;34,"VERIF. ESBELTEZ","VERIFICA")))))</f>
         <v/>
       </c>
       <c r="N15" s="18" t="inlineStr">
         <is>
-          <t>COL 02 del plano. Carga estimada por bajada automatica: 42.1 t (incompleta, ver Memoria).</t>
+          <t>COL 02 del plano. Carga PROVISORIA por bajada automatica; es un piso, la real es mayor (ver Memoria, punto 5).</t>
         </is>
       </c>
       <c r="O15" s="19">
@@ -1751,7 +1775,9 @@
       <c r="C16" s="24" t="n">
         <v>3.15</v>
       </c>
-      <c r="D16" s="25" t="n"/>
+      <c r="D16" s="25" t="n">
+        <v>49.51</v>
+      </c>
       <c r="E16" s="26" t="n">
         <v>15</v>
       </c>
@@ -1780,12 +1806,12 @@
         <v/>
       </c>
       <c r="M16" s="27">
-        <f>IF(D16="","FALTA CARGA",IF(O16&lt;H16,"ARM. INSUFIC.",IF(D16&gt;P16,"NO VERIFICA",IF(Q16&gt;34,"VERIF. ESBELTEZ","VERIFICA"))))</f>
+        <f>IF(D16="","FALTA CARGA",IF(O16&lt;H16,"ARM. INSUFIC.",IF(D16&gt;P16,"NO VERIFICA",IF(D16&gt;0.85*P16,"AL LIMITE",IF(Q16&gt;34,"VERIF. ESBELTEZ","VERIFICA")))))</f>
         <v/>
       </c>
       <c r="N16" s="29" t="inlineStr">
         <is>
-          <t>COL 02 del plano. Carga estimada por bajada automatica: 49.5 t (incompleta, ver Memoria).</t>
+          <t>COL 02 del plano. Carga PROVISORIA por bajada automatica; es un piso, la real es mayor (ver Memoria, punto 5).</t>
         </is>
       </c>
       <c r="O16" s="30">
@@ -1836,6 +1862,9 @@
     <cfRule type="cellIs" priority="5" operator="equal" dxfId="1">
       <formula>"FALTA CARGA"</formula>
     </cfRule>
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="1">
+      <formula>"AL LIMITE"</formula>
+    </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation sqref="J4:J16 K4:K16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -1853,7 +1882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:B46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2043,12 +2072,12 @@
     <row r="24">
       <c r="A24" s="33" t="inlineStr">
         <is>
-          <t>5. CARGAS: FALTA</t>
+          <t>5. CARGAS</t>
         </is>
       </c>
       <c r="B24" s="33" t="inlineStr">
         <is>
-          <t>La columna CARGA (t) esta VACIA y hay que completarla. En la columna auxiliar</t>
+          <t>La columna CARGA (t) viene cargada con una bajada automatica: suma de las</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2085,7 @@
       <c r="A25" s="33" t="inlineStr"/>
       <c r="B25" s="34" t="inlineStr">
         <is>
-          <t>carga estim. se deja una bajada automatica, hecha sumando las reacciones de las</t>
+          <t>reacciones de las vigas que apoyan en cada columna (tomadas de la planilla de</t>
         </is>
       </c>
     </row>
@@ -2064,7 +2093,7 @@
       <c r="A26" s="33" t="inlineStr"/>
       <c r="B26" s="34" t="inlineStr">
         <is>
-          <t>vigas ya calculadas mas el peso propio y lo que baja del nivel superior.</t>
+          <t>vigas), mas el peso propio, mas lo que baja de la columna del nivel superior.</t>
         </is>
       </c>
     </row>
@@ -2072,7 +2101,7 @@
       <c r="A27" s="33" t="inlineStr"/>
       <c r="B27" s="34" t="inlineStr">
         <is>
-          <t>ESA ESTIMACION ES UN PISO, NO EL VALOR REAL: 20 de los 60 extremos de viga no</t>
+          <t>ES UNA CARGA PROVISORIA Y ES UN PISO, NO EL VALOR REAL: 20 de los 60 extremos</t>
         </is>
       </c>
     </row>
@@ -2080,7 +2109,7 @@
       <c r="A28" s="33" t="inlineStr"/>
       <c r="B28" s="34" t="inlineStr">
         <is>
-          <t>pudieron asignarse a ninguna columna (apoyan en otra viga, en un tabique o en la</t>
+          <t>de viga no pudieron asignarse a ninguna columna porque apoyan en otra viga, en</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2117,7 @@
       <c r="A29" s="33" t="inlineStr"/>
       <c r="B29" s="34" t="inlineStr">
         <is>
-          <t>medianera), y esas reacciones no estan sumadas. La carga real es mayor.</t>
+          <t>un tabique o en la medianera, y esas reacciones no estan sumadas.</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2125,7 @@
       <c r="A30" s="33" t="inlineStr"/>
       <c r="B30" s="34" t="inlineStr">
         <is>
-          <t>Ademas son cargas MAYORADAS, coherentes con la planilla de vigas. Si la catedra</t>
+          <t>Para cerrarla hay que indicar, para cada uno de esos 20 extremos, en que apoya.</t>
         </is>
       </c>
     </row>
@@ -2104,39 +2133,39 @@
       <c r="A31" s="33" t="inlineStr"/>
       <c r="B31" s="34" t="inlineStr">
         <is>
-          <t>pide cargas de servicio, dividir por el coeficiente que corresponda.</t>
+          <t>Mientras tanto la columna es editable: al corregir un valor todo recalcula.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="33" t="inlineStr"/>
-      <c r="B32" s="34" t="inlineStr"/>
+      <c r="B32" s="34" t="inlineStr">
+        <is>
+          <t>Ademas son cargas MAYORADAS, coherentes con la planilla de vigas. Si la catedra</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="33" t="inlineStr">
-        <is>
-          <t>6. ESBELTEZ</t>
-        </is>
-      </c>
-      <c r="B33" s="33" t="inlineStr">
-        <is>
-          <t>Todas las columnas son esbeltas: con lado menor de 15 cm y 3,15 m de altura,</t>
+      <c r="A33" s="33" t="inlineStr"/>
+      <c r="B33" s="34" t="inlineStr">
+        <is>
+          <t>pide cargas de servicio, dividir por el coeficiente que corresponda.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="33" t="inlineStr"/>
-      <c r="B34" s="34" t="inlineStr">
-        <is>
-          <t>k lu / r = 70, muy por encima del limite de 34 por debajo del cual se puede</t>
-        </is>
-      </c>
+      <c r="B34" s="34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="33" t="inlineStr"/>
-      <c r="B35" s="34" t="inlineStr">
-        <is>
-          <t>despreciar el pandeo. En la practica el llenado de mamposteria las arriostra, pero</t>
+      <c r="A35" s="33" t="inlineStr">
+        <is>
+          <t>6. ESBELTEZ</t>
+        </is>
+      </c>
+      <c r="B35" s="33" t="inlineStr">
+        <is>
+          <t>Todas las columnas son esbeltas: con lado menor de 15 cm y 3,15 m de altura,</t>
         </is>
       </c>
     </row>
@@ -2144,69 +2173,85 @@
       <c r="A36" s="33" t="inlineStr"/>
       <c r="B36" s="34" t="inlineStr">
         <is>
-          <t>si la catedra lo pide hay que verificar segundo orden. La planilla lo marca.</t>
+          <t>k lu / r = 70, muy por encima del limite de 34 por debajo del cual se puede</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="33" t="inlineStr"/>
-      <c r="B37" s="34" t="inlineStr"/>
+      <c r="B37" s="34" t="inlineStr">
+        <is>
+          <t>despreciar el pandeo. En la practica el llenado de mamposteria las arriostra, pero</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="33" t="inlineStr">
-        <is>
-          <t>7. C4, A REVISAR</t>
-        </is>
-      </c>
-      <c r="B38" s="33" t="inlineStr">
-        <is>
-          <t>C4 figura en el plano como 10x10 y recibe el extremo de VI 01a, con 17 t de</t>
+      <c r="A38" s="33" t="inlineStr"/>
+      <c r="B38" s="34" t="inlineStr">
+        <is>
+          <t>si la catedra lo pide hay que verificar segundo orden. La planilla lo marca.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="33" t="inlineStr"/>
-      <c r="B39" s="34" t="inlineStr">
-        <is>
-          <t>reaccion. Una columna de 10x10 no toma esa carga. VI 01a corre sobre la medianera,</t>
-        </is>
-      </c>
+      <c r="B39" s="34" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="33" t="inlineStr"/>
-      <c r="B40" s="34" t="inlineStr">
-        <is>
-          <t>asi que lo mas probable es que apoye en el muro y ese 10x10 no sea una columna.</t>
+      <c r="A40" s="33" t="inlineStr">
+        <is>
+          <t>7. C4, A REVISAR</t>
+        </is>
+      </c>
+      <c r="B40" s="33" t="inlineStr">
+        <is>
+          <t>C4 figura en el plano como 10x10 y recibe el extremo de VI 01a, con 17 t de</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="33" t="inlineStr"/>
-      <c r="B41" s="34" t="inlineStr"/>
+      <c r="B41" s="34" t="inlineStr">
+        <is>
+          <t>reaccion. Una columna de 10x10 no toma esa carga. VI 01a corre sobre la medianera,</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="33" t="inlineStr">
-        <is>
-          <t>LIMITACIONES</t>
-        </is>
-      </c>
-      <c r="B42" s="33" t="inlineStr">
-        <is>
-          <t>Trabajo academico. Requiere verificacion y firma de profesional matriculado.</t>
+      <c r="A42" s="33" t="inlineStr"/>
+      <c r="B42" s="34" t="inlineStr">
+        <is>
+          <t>asi que lo mas probable es que apoye en el muro y ese 10x10 no sea una columna.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="33" t="inlineStr"/>
-      <c r="B43" s="34" t="inlineStr">
+      <c r="B43" s="34" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="33" t="inlineStr">
+        <is>
+          <t>LIMITACIONES</t>
+        </is>
+      </c>
+      <c r="B44" s="33" t="inlineStr">
+        <is>
+          <t>Trabajo academico. Requiere verificacion y firma de profesional matriculado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="33" t="inlineStr"/>
+      <c r="B45" s="34" t="inlineStr">
         <is>
           <t>No se verifica flexion compuesta: las columnas de borde reciben momento de las</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="33" t="inlineStr"/>
-      <c r="B44" s="34" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="33" t="inlineStr"/>
+      <c r="B46" s="34" t="inlineStr">
         <is>
           <t>vigas invertidas y trabajan a flexo-compresion, no a compresion simple.</t>
         </is>

--- a/planillas/planilla_columnas.xlsx
+++ b/planillas/planilla_columnas.xlsx
@@ -1451,7 +1451,7 @@
         <v>3.15</v>
       </c>
       <c r="D11" s="15" t="n">
-        <v>28.77</v>
+        <v>17.61</v>
       </c>
       <c r="E11" s="16" t="n">
         <v>10</v>
@@ -1502,7 +1502,7 @@
         <v/>
       </c>
       <c r="R11" s="19" t="n">
-        <v>28.77</v>
+        <v>17.61</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">

--- a/planillas/planilla_columnas.xlsx
+++ b/planillas/planilla_columnas.xlsx
@@ -992,7 +992,7 @@
         <v>3.22</v>
       </c>
       <c r="D4" s="15" t="n">
-        <v>14.25</v>
+        <v>12.71</v>
       </c>
       <c r="E4" s="16" t="n">
         <v>20</v>
@@ -1043,7 +1043,7 @@
         <v/>
       </c>
       <c r="R4" s="19" t="n">
-        <v>14.25</v>
+        <v>12.71</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
@@ -1057,7 +1057,7 @@
         <v>3.22</v>
       </c>
       <c r="D5" s="15" t="n">
-        <v>17.23</v>
+        <v>22.06</v>
       </c>
       <c r="E5" s="16" t="n">
         <v>30</v>
@@ -1108,7 +1108,7 @@
         <v/>
       </c>
       <c r="R5" s="19" t="n">
-        <v>17.23</v>
+        <v>22.06</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
@@ -1122,7 +1122,7 @@
         <v>3.22</v>
       </c>
       <c r="D6" s="15" t="n">
-        <v>18.5</v>
+        <v>15.12</v>
       </c>
       <c r="E6" s="16" t="n">
         <v>15</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="R6" s="19" t="n">
-        <v>18.5</v>
+        <v>15.12</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
@@ -1187,7 +1187,7 @@
         <v>3.22</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>19.44</v>
+        <v>20.05</v>
       </c>
       <c r="E7" s="26" t="n">
         <v>15</v>
@@ -1238,7 +1238,7 @@
         <v/>
       </c>
       <c r="R7" s="30" t="n">
-        <v>19.44</v>
+        <v>20.05</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
@@ -1256,7 +1256,7 @@
         <v>3.15</v>
       </c>
       <c r="D8" s="15" t="n">
-        <v>6.38</v>
+        <v>2.49</v>
       </c>
       <c r="E8" s="16" t="n">
         <v>15</v>
@@ -1307,7 +1307,7 @@
         <v/>
       </c>
       <c r="R8" s="19" t="n">
-        <v>6.38</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
@@ -1321,7 +1321,7 @@
         <v>3.15</v>
       </c>
       <c r="D9" s="15" t="n">
-        <v>36.41</v>
+        <v>29.47</v>
       </c>
       <c r="E9" s="16" t="n">
         <v>15</v>
@@ -1372,7 +1372,7 @@
         <v/>
       </c>
       <c r="R9" s="19" t="n">
-        <v>36.41</v>
+        <v>29.47</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
@@ -1386,7 +1386,7 @@
         <v>3.15</v>
       </c>
       <c r="D10" s="15" t="n">
-        <v>19.85</v>
+        <v>10.6</v>
       </c>
       <c r="E10" s="16" t="n">
         <v>30</v>
@@ -1437,7 +1437,7 @@
         <v/>
       </c>
       <c r="R10" s="19" t="n">
-        <v>19.85</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
@@ -1451,7 +1451,7 @@
         <v>3.15</v>
       </c>
       <c r="D11" s="15" t="n">
-        <v>17.61</v>
+        <v>10.28</v>
       </c>
       <c r="E11" s="16" t="n">
         <v>10</v>
@@ -1502,7 +1502,7 @@
         <v/>
       </c>
       <c r="R11" s="19" t="n">
-        <v>17.61</v>
+        <v>10.28</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
@@ -1516,7 +1516,7 @@
         <v>3.15</v>
       </c>
       <c r="D12" s="15" t="n">
-        <v>20.2</v>
+        <v>15.9</v>
       </c>
       <c r="E12" s="16" t="n">
         <v>15</v>
@@ -1567,7 +1567,7 @@
         <v/>
       </c>
       <c r="R12" s="19" t="n">
-        <v>20.2</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -1581,7 +1581,7 @@
         <v>3.15</v>
       </c>
       <c r="D13" s="15" t="n">
-        <v>43.36</v>
+        <v>32.1</v>
       </c>
       <c r="E13" s="16" t="n">
         <v>20</v>
@@ -1632,7 +1632,7 @@
         <v/>
       </c>
       <c r="R13" s="19" t="n">
-        <v>43.36</v>
+        <v>32.1</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
@@ -1646,7 +1646,7 @@
         <v>3.15</v>
       </c>
       <c r="D14" s="15" t="n">
-        <v>32.38</v>
+        <v>37.23</v>
       </c>
       <c r="E14" s="16" t="n">
         <v>30</v>
@@ -1697,7 +1697,7 @@
         <v/>
       </c>
       <c r="R14" s="19" t="n">
-        <v>32.38</v>
+        <v>37.23</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
@@ -1711,7 +1711,7 @@
         <v>3.15</v>
       </c>
       <c r="D15" s="15" t="n">
-        <v>42.14</v>
+        <v>43.4</v>
       </c>
       <c r="E15" s="16" t="n">
         <v>15</v>
@@ -1762,7 +1762,7 @@
         <v/>
       </c>
       <c r="R15" s="19" t="n">
-        <v>42.14</v>
+        <v>43.4</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
@@ -1776,7 +1776,7 @@
         <v>3.15</v>
       </c>
       <c r="D16" s="25" t="n">
-        <v>49.51</v>
+        <v>54.69</v>
       </c>
       <c r="E16" s="26" t="n">
         <v>15</v>
@@ -1827,7 +1827,7 @@
         <v/>
       </c>
       <c r="R16" s="30" t="n">
-        <v>49.51</v>
+        <v>54.69</v>
       </c>
     </row>
   </sheetData>

--- a/planillas/planilla_columnas.xlsx
+++ b/planillas/planilla_columnas.xlsx
@@ -1711,7 +1711,7 @@
         <v>3.15</v>
       </c>
       <c r="D15" s="15" t="n">
-        <v>43.4</v>
+        <v>42.22</v>
       </c>
       <c r="E15" s="16" t="n">
         <v>15</v>
@@ -1762,7 +1762,7 @@
         <v/>
       </c>
       <c r="R15" s="19" t="n">
-        <v>43.4</v>
+        <v>42.22</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">

--- a/planillas/planilla_columnas.xlsx
+++ b/planillas/planilla_columnas.xlsx
@@ -1646,7 +1646,7 @@
         <v>3.15</v>
       </c>
       <c r="D14" s="15" t="n">
-        <v>37.23</v>
+        <v>37.27</v>
       </c>
       <c r="E14" s="16" t="n">
         <v>30</v>
@@ -1697,7 +1697,7 @@
         <v/>
       </c>
       <c r="R14" s="19" t="n">
-        <v>37.23</v>
+        <v>37.27</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
@@ -1776,7 +1776,7 @@
         <v>3.15</v>
       </c>
       <c r="D16" s="25" t="n">
-        <v>54.69</v>
+        <v>54.89</v>
       </c>
       <c r="E16" s="26" t="n">
         <v>15</v>
@@ -1827,7 +1827,7 @@
         <v/>
       </c>
       <c r="R16" s="30" t="n">
-        <v>54.69</v>
+        <v>54.89</v>
       </c>
     </row>
   </sheetData>
